--- a/src/MultiPeriodCalculator.Console/Files/mpcf.xlsx
+++ b/src/MultiPeriodCalculator.Console/Files/mpcf.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e4a1e422fcefc39/private/dev/PensionTools/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\MultiPeriodCalculator.Console\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="341" documentId="11_F25DC773A252ABDACC1048DFE15F5DAA5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8B488A4-C8FF-4118-BEEC-7041A3CF11EE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE85CD95-FB2A-43E9-8D04-AA0011335ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20730" yWindow="135" windowWidth="19485" windowHeight="19200" tabRatio="598" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14115" yWindow="135" windowWidth="26100" windowHeight="19200" tabRatio="598" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>

--- a/src/MultiPeriodCalculator.Console/Files/mpcf.xlsx
+++ b/src/MultiPeriodCalculator.Console/Files/mpcf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\MultiPeriodCalculator.Console\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE85CD95-FB2A-43E9-8D04-AA0011335ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38FEFD1-0E81-4129-86FA-23348CADB0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14115" yWindow="135" windowWidth="26100" windowHeight="19200" tabRatio="598" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20520" yWindow="1095" windowWidth="30630" windowHeight="19200" tabRatio="598" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>

--- a/src/MultiPeriodCalculator.Console/Files/mpcf.xlsx
+++ b/src/MultiPeriodCalculator.Console/Files/mpcf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\MultiPeriodCalculator.Console\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38FEFD1-0E81-4129-86FA-23348CADB0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712809FF-8CFD-411B-9B5C-9EFDA23A1C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20520" yWindow="1095" windowWidth="30630" windowHeight="19200" tabRatio="598" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20520" yWindow="1095" windowWidth="30630" windowHeight="19200" tabRatio="598" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -232,6 +232,15 @@
   </si>
   <si>
     <t>Steuer-Id</t>
+  </si>
+  <si>
+    <t># Lohnzahlungen</t>
+  </si>
+  <si>
+    <t># Setup Kontosaldi</t>
+  </si>
+  <si>
+    <t># Exogene Konti</t>
   </si>
 </sst>
 </file>
@@ -752,7 +761,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -773,32 +782,32 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
@@ -806,58 +815,53 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4</v>
+        <f>A4+1</f>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <f>A5+1</f>
-        <v>5</v>
+        <f>A13+1</f>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <f t="shared" ref="A7:A21" si="0">A6+1</f>
-        <v>6</v>
+        <f>A12+1</f>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
@@ -865,11 +869,11 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>A6+1</f>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -877,11 +881,11 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" ref="A11:A22" si="0">A10+1</f>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -890,22 +894,22 @@
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>A5+1</f>
+        <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>18</v>
@@ -913,16 +917,20 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+        <f>A7+1</f>
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -930,7 +938,7 @@
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -938,7 +946,7 @@
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -946,7 +954,7 @@
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -954,7 +962,7 @@
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -962,7 +970,7 @@
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -970,17 +978,25 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Kontotyp" sqref="C22:C42" xr:uid="{D4AE15E6-E34E-49B0-8D78-41004BD608AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Kontotyp" sqref="C23:C43" xr:uid="{D4AE15E6-E34E-49B0-8D78-41004BD608AD}">
       <formula1>"Income, Wealth, Exogenous, Third Pillar, Occupational Pension"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Kontotyp" sqref="C2:C21" xr:uid="{EC0365FF-A8E0-40EE-B4D4-4AAD994A3356}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Kontotyp" sqref="C6:C22 C2:C5" xr:uid="{EC0365FF-A8E0-40EE-B4D4-4AAD994A3356}">
       <formula1>"Lohn, Vermögen, Exogenous, 3a, PK"</formula1>
     </dataValidation>
   </dataValidations>
@@ -990,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6223A4C6-1802-4880-8580-86AB5C9C2946}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -1026,27 +1042,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>45292</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>200000</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
+      <c r="A2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -1056,13 +1060,13 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>80000</v>
+        <v>200000</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1073,19 +1077,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>45658</v>
+        <v>45292</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>10000</v>
+        <v>80000</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -1173,7 +1177,7 @@
         <v>45658</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1182,18 +1186,18 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>1600</v>
+        <v>10000</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -1216,53 +1220,35 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>45292</v>
+        <v>46023</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>50000</v>
+        <v>1600</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>45474</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>11</v>
-      </c>
-      <c r="E12">
-        <v>50000</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
+      <c r="A12" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45658</v>
+        <v>45292</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
@@ -1285,7 +1271,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45839</v>
+        <v>45474</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
@@ -1308,7 +1294,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
@@ -1331,7 +1317,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46204</v>
+        <v>45839</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
@@ -1354,53 +1340,53 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>45657</v>
+        <v>46023</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46022</v>
+        <v>46204</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46387</v>
+        <v>45657</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
@@ -1418,6 +1404,52 @@
         <v>12</v>
       </c>
       <c r="G19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>40000</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>46387</v>
+      </c>
+      <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>12</v>
+      </c>
+      <c r="E21">
+        <v>40000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
         <v>36</v>
       </c>
     </row>
